--- a/data/trans_dic/IP1002-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1002-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen bornquitis crónica</t>
+          <t>Menores que padecen bornquitis crónica (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,45</t>
+          <t>0,0; 4,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,6</t>
+          <t>0,0; 3,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,21</t>
+          <t>0,0; 3,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 6,67</t>
+          <t>0,58; 6,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,23</t>
+          <t>0,0; 4,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,5</t>
+          <t>0,63; 6,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,53</t>
+          <t>0,0; 1,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>0,0; 2,07</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>0,0; 2,65</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,52</t>
+          <t>0,37; 3,15</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,08</t>
+          <t>0,46; 2,98</t>
         </is>
       </c>
     </row>
@@ -856,42 +857,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,84</t>
+          <t>0,0; 6,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,12</t>
+          <t>0,0; 3,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,04</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,5</t>
+          <t>0,0; 6,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,16</t>
+          <t>0,69; 5,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,7</t>
+          <t>0,0; 4,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 9,64</t>
+          <t>0,9; 9,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -901,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,24</t>
+          <t>0,36; 3,48</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,28</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 5,67</t>
+          <t>0,66; 4,95</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,32</t>
+          <t>0,0; 4,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,83</t>
+          <t>0,0; 5,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,97</t>
+          <t>0,0; 4,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,93</t>
+          <t>0,0; 4,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,32</t>
+          <t>0,0; 5,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,64</t>
+          <t>0,0; 11,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,69</t>
+          <t>0,0; 2,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,67</t>
+          <t>0,37; 3,58</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,19</t>
+          <t>0,0; 2,31</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,63</t>
+          <t>0,0; 5,8</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,97</t>
+          <t>0,32; 2,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,54</t>
+          <t>0,98; 4,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,81</t>
+          <t>0,85; 4,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,53</t>
+          <t>0,34; 3,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,47</t>
+          <t>0,73; 4,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,34; 7,56</t>
+          <t>2,35; 7,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,94</t>
+          <t>0,3; 2,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,41</t>
+          <t>0,37; 3,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,97</t>
+          <t>0,82; 2,94</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,01; 5,04</t>
+          <t>2,05; 5,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,87</t>
+          <t>0,85; 2,83</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,69</t>
+          <t>0,57; 2,73</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 6,08</t>
+          <t>0,61; 6,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,53</t>
+          <t>0,9; 5,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,21</t>
+          <t>0,44; 4,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 5,5</t>
+          <t>0,33; 5,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,72</t>
+          <t>0,0; 2,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,52</t>
+          <t>0,0; 3,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,94</t>
+          <t>0,45; 4,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,19</t>
+          <t>0,24; 3,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,3</t>
+          <t>0,54; 3,52</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,38</t>
+          <t>0,72; 3,29</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,22</t>
+          <t>0,57; 3,16</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,12</t>
+          <t>0,59; 3,45</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,72</t>
+          <t>0,0; 4,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,54</t>
+          <t>0,0; 3,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,97</t>
+          <t>0,0; 5,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,06</t>
+          <t>0,0; 5,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,47</t>
+          <t>0,0; 6,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,02</t>
+          <t>0,0; 5,51</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,47</t>
+          <t>0,0; 2,79</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,12</t>
+          <t>0,0; 3,84</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,9</t>
+          <t>0,0; 2,92</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,69</t>
+          <t>0,0; 3,49</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,22</t>
+          <t>0,72; 2,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,53</t>
+          <t>0,97; 2,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,95</t>
+          <t>0,61; 2,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,27</t>
+          <t>0,74; 2,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,0</t>
+          <t>0,58; 2,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,45</t>
+          <t>1,5; 3,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,13</t>
+          <t>0,75; 2,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,64</t>
+          <t>0,77; 2,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,8</t>
+          <t>0,81; 1,8</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,58</t>
+          <t>1,45; 2,73</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,78</t>
+          <t>0,83; 1,8</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,02</t>
+          <t>0,87; 2,05</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen bornquitis crónica (tasa de respuesta: 99,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1331</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>703</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1331</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1373</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2553</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3115</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4237</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3358</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2808</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>607; 6490</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4022</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>630; 6064</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 1845</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4175</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4731</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>683; 5754</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1121; 7200</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1328</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1515</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2137</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1386</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>3409</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2842</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2705</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1386</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3831</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5321</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3200</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2142</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5287</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>663; 5313</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4645</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>860; 9517</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>708; 6790</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>675; 6566</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5028</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>1262; 9421</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1559</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1375</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2625</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1559</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3229</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4547</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4028</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4211</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3800</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 7302</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4790</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>635; 6123</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3167</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 6710</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2385</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4489</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3052</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4173</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>9712</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2603</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>6558</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>14388</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>6989</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>5655</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>639; 5927</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2022; 9254</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1892; 8978</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>751; 7974</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1472; 8902</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>5332; 16296</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>628; 5675</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>806; 7425</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>3305; 11825</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>8883; 21814</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3699; 12280</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2492; 11869</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2627</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3557</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2125</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2114</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1364</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1826</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3353</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>4921</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>4260</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>3939</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>632; 6761</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1348; 8113</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>602; 5994</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>393; 6725</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3602</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5374</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>648; 5868</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>391; 6071</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1260; 8146</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2080; 9496</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>1590; 8825</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>1671; 9719</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1326</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>863</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1326</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>1254</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3041</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2433</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3641</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4377</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4281</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3969</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4105</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4916</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3770</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4922</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>8345</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>10777</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>7714</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>8698</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>7842</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>16561</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>9313</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>10656</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>16187</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>27338</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>17027</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>19354</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>4620; 14180</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>6544; 17490</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>4067; 13508</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>4862; 15632</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>3972; 14439</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>10705; 24470</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>5328; 14615</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>5784; 18299</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>10720; 23794</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>20155; 37843</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>11463; 24919</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>12283; 28858</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1002-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1002-Clase-trans_dic.xlsx
@@ -717,22 +717,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,06</t>
+          <t>0,0; 4,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,8</t>
+          <t>0,0; 3,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,38</t>
+          <t>0,0; 3,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 6,21</t>
+          <t>0,58; 5,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,48</t>
+          <t>0,0; 4,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,08</t>
+          <t>0,64; 5,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,35</t>
+          <t>0,0; 1,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>0,0; 2,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,65</t>
+          <t>0,0; 2,68</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,15</t>
+          <t>0,35; 3,43</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,98</t>
+          <t>0,46; 3,02</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,09</t>
+          <t>0,0; 4,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,45</t>
+          <t>0,0; 3,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,47 +872,47 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>0,0; 2,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,15</t>
+          <t>0,0; 6,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 5,53</t>
+          <t>0,69; 6,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,12</t>
+          <t>0,0; 4,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 9,96</t>
+          <t>0,9; 10,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,92</t>
+          <t>0,49; 4,03</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,48</t>
+          <t>0,36; 3,79</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,95</t>
+          <t>0,45; 5,39</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,79</t>
+          <t>0,0; 5,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,4</t>
+          <t>0,0; 6,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1017,42 +1017,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,06</t>
+          <t>0,0; 4,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,85</t>
+          <t>0,0; 5,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,04</t>
+          <t>0,0; 4,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,44</t>
+          <t>0,0; 13,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,87</t>
+          <t>0,0; 2,77</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,58</t>
+          <t>0,39; 3,85</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,31</t>
+          <t>0,0; 2,32</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,8</t>
+          <t>0,0; 7,73</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,95</t>
+          <t>0,32; 2,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,5</t>
+          <t>0,93; 4,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,02</t>
+          <t>0,88; 4,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,66</t>
+          <t>0,37; 3,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,41</t>
+          <t>0,93; 4,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,35; 7,18</t>
+          <t>2,31; 6,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,69</t>
+          <t>0,3; 2,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,42</t>
+          <t>0,37; 3,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,94</t>
+          <t>0,79; 2,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 5,04</t>
+          <t>2,11; 5,13</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,83</t>
+          <t>0,83; 2,78</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,73</t>
+          <t>0,56; 2,59</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 6,49</t>
+          <t>0,83; 6,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,44</t>
+          <t>0,85; 5,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,4</t>
+          <t>0,45; 4,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 5,63</t>
+          <t>0,34; 5,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,83</t>
+          <t>0,0; 2,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,84</t>
+          <t>0,0; 3,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,1</t>
+          <t>0,45; 3,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,73</t>
+          <t>0,24; 3,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,52</t>
+          <t>0,53; 3,61</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,29</t>
+          <t>0,74; 3,33</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,16</t>
+          <t>0,53; 3,11</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,45</t>
+          <t>0,53; 3,19</t>
         </is>
       </c>
     </row>
@@ -1427,52 +1427,52 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,98</t>
+          <t>0,0; 3,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,53</t>
+          <t>0,0; 3,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,03</t>
+          <t>0,0; 5,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,91</t>
+          <t>0,0; 6,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,31</t>
+          <t>0,0; 4,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,51</t>
+          <t>0,0; 6,05</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,79</t>
+          <t>0,0; 2,75</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,84</t>
+          <t>0,0; 3,67</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,92</t>
+          <t>0,0; 2,91</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,49</t>
+          <t>0,0; 3,23</t>
         </is>
       </c>
     </row>
@@ -1557,27 +1557,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,22</t>
+          <t>0,67; 2,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,59</t>
+          <t>0,89; 2,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,01</t>
+          <t>0,63; 2,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,38</t>
+          <t>0,68; 2,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,11</t>
+          <t>0,59; 1,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1587,32 +1587,32 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,06</t>
+          <t>0,73; 2,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,45</t>
+          <t>0,74; 2,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,8</t>
+          <t>0,79; 1,79</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,73</t>
+          <t>1,4; 2,66</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,8</t>
+          <t>0,81; 1,77</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,05</t>
+          <t>0,9; 1,99</t>
         </is>
       </c>
     </row>
@@ -1927,22 +1927,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4237</t>
+          <t>0; 4401</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3358</t>
+          <t>0; 3162</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2808</t>
+          <t>0; 2751</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>607; 6490</t>
+          <t>602; 6020</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1952,37 +1952,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4022</t>
+          <t>0; 3732</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>630; 6064</t>
+          <t>637; 5419</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 1845</t>
+          <t>0; 2369</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4175</t>
+          <t>0; 4502</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 4731</t>
+          <t>0; 4783</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>683; 5754</t>
+          <t>635; 6280</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1121; 7200</t>
+          <t>1122; 7295</t>
         </is>
       </c>
     </row>
@@ -2135,12 +2135,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5321</t>
+          <t>0; 4190</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3200</t>
+          <t>0; 2864</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2150,47 +2150,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2142</t>
+          <t>0; 2344</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5287</t>
+          <t>0; 5243</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>663; 5313</t>
+          <t>662; 6043</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4645</t>
+          <t>0; 4785</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>860; 9517</t>
+          <t>856; 10334</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>708; 6790</t>
+          <t>844; 6990</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>675; 6566</t>
+          <t>672; 7162</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5028</t>
+          <t>0; 5358</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1262; 9421</t>
+          <t>853; 10251</t>
         </is>
       </c>
     </row>
@@ -2343,12 +2343,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3229</t>
+          <t>0; 3863</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4547</t>
+          <t>0; 5262</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2363,42 +2363,42 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4028</t>
+          <t>0; 4206</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4211</t>
+          <t>0; 4414</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3800</t>
+          <t>0; 3178</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 7302</t>
+          <t>0; 8314</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4790</t>
+          <t>0; 4622</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>635; 6123</t>
+          <t>671; 6590</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 3167</t>
+          <t>0; 3182</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 6710</t>
+          <t>0; 8947</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>639; 5927</t>
+          <t>636; 5947</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2022; 9254</t>
+          <t>1904; 9139</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1892; 8978</t>
+          <t>1963; 9517</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>751; 7974</t>
+          <t>816; 8305</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1472; 8902</t>
+          <t>1885; 8700</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5332; 16296</t>
+          <t>5243; 15746</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>628; 5675</t>
+          <t>631; 6280</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>806; 7425</t>
+          <t>802; 7561</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3305; 11825</t>
+          <t>3190; 11579</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8883; 21814</t>
+          <t>9123; 22208</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3699; 12280</t>
+          <t>3620; 12076</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2492; 11869</t>
+          <t>2419; 11283</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>632; 6761</t>
+          <t>864; 6742</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1348; 8113</t>
+          <t>1273; 8041</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>602; 5994</t>
+          <t>609; 6142</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>393; 6725</t>
+          <t>405; 6145</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3602</t>
+          <t>0; 3641</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 5374</t>
+          <t>0; 4844</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>648; 5868</t>
+          <t>650; 5668</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>391; 6071</t>
+          <t>394; 5361</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1260; 8146</t>
+          <t>1218; 8364</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2080; 9496</t>
+          <t>2144; 9614</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1590; 8825</t>
+          <t>1475; 8681</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1671; 9719</t>
+          <t>1506; 8999</t>
         </is>
       </c>
     </row>
@@ -2977,52 +2977,52 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3041</t>
+          <t>0; 2327</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2433</t>
+          <t>0; 2229</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3641</t>
+          <t>0; 4321</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 4377</t>
+          <t>0; 4641</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 4281</t>
+          <t>0; 2721</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3969</t>
+          <t>0; 4358</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 4105</t>
+          <t>0; 4050</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 4916</t>
+          <t>0; 4697</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 3770</t>
+          <t>0; 3752</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 4922</t>
+          <t>0; 4546</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4620; 14180</t>
+          <t>4301; 13632</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6544; 17490</t>
+          <t>5987; 17027</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4067; 13508</t>
+          <t>4234; 13572</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4862; 15632</t>
+          <t>4440; 14243</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3972; 14439</t>
+          <t>4031; 13485</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10705; 24470</t>
+          <t>10719; 24458</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5328; 14615</t>
+          <t>5211; 15460</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5784; 18299</t>
+          <t>5551; 20229</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10720; 23794</t>
+          <t>10422; 23671</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>20155; 37843</t>
+          <t>19447; 36892</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11463; 24919</t>
+          <t>11184; 24478</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>12283; 28858</t>
+          <t>12704; 28012</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1002-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1002-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1,28%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,76%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,64%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,58</t>
+          <t>0,0; 4,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,31</t>
+          <t>0,63; 5,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,76</t>
+          <t>0,0; 1,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,16</t>
+          <t>0,0; 4,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,43</t>
+          <t>0,0; 4,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,73</t>
+          <t>0,86; 7,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,23</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,68</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,43</t>
+          <t>0,37; 3,52</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,02</t>
+          <t>0,49; 3,29</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3,76%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>1,52%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,61%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,79</t>
+          <t>0,0; 5,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,09</t>
+          <t>0,7; 6,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 4,7</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0,97; 10,16</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 4,84</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 3,12</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,48</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,1</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,69; 6,29</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,24</t>
-        </is>
-      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 10,81</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,03</t>
+          <t>0,41; 3,92</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,79</t>
+          <t>0,36; 3,24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,45</t>
+          <t>0,0; 2,28</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 5,39</t>
+          <t>0,65; 5,82</t>
         </is>
       </c>
     </row>
@@ -929,44 +929,44 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,55%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>0,82%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,73</t>
+          <t>0,0; 3,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,25</t>
+          <t>0,0; 4,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 4,32</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 9,12</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 7,32</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 4,83</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,23</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,08</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,21</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 13,02</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,77</t>
+          <t>0,0; 2,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,85</t>
+          <t>0,37; 3,67</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,32</t>
+          <t>0,0; 2,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,73</t>
+          <t>0,0; 4,5</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,28%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>1,19%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,27%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2,01%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,96</t>
+          <t>0,94; 4,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,44</t>
+          <t>2,34; 7,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,26</t>
+          <t>0,3; 2,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,81</t>
+          <t>0,37; 3,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,31</t>
+          <t>0,39; 2,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,94</t>
+          <t>0,92; 4,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,98</t>
+          <t>0,9; 3,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,48</t>
+          <t>0,48; 4,44</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,87</t>
+          <t>0,8; 2,97</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 5,13</t>
+          <t>2,01; 5,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,78</t>
+          <t>0,89; 2,87</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,59</t>
+          <t>0,67; 3,26</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>2,52%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,38%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,56%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 6,48</t>
+          <t>0,0; 3,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,39</t>
+          <t>0,0; 3,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,51</t>
+          <t>0,46; 3,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 5,15</t>
+          <t>0,2; 3,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,86</t>
+          <t>0,57; 6,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,46</t>
+          <t>0,88; 5,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,96</t>
+          <t>0,44; 4,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,3</t>
+          <t>0,43; 5,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,61</t>
+          <t>0,53; 3,3</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,33</t>
+          <t>0,72; 3,38</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,11</t>
+          <t>0,62; 3,22</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,19</t>
+          <t>0,53; 3,24</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>0,92%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>0,0; 4,97</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 6,06</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 5,47</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 6,63</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,81</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,24</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,97</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,27</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,01</t>
+          <t>0,0; 4,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,05</t>
+          <t>0,0; 2,23</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,75</t>
+          <t>0,0; 2,47</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,67</t>
+          <t>0,0; 3,12</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,91</t>
+          <t>0,0; 2,9</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,23</t>
+          <t>0,0; 3,87</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>1,31%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1,6%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>1,15%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,13</t>
+          <t>0,62; 2,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,53</t>
+          <t>1,51; 3,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,02</t>
+          <t>0,75; 2,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,17</t>
+          <t>0,73; 2,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,97</t>
+          <t>0,75; 2,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,43</t>
+          <t>0,95; 2,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,18</t>
+          <t>0,62; 1,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,7</t>
+          <t>0,75; 2,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,79</t>
+          <t>0,82; 1,8</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,66</t>
+          <t>1,37; 2,58</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,77</t>
+          <t>0,81; 1,78</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,99</t>
+          <t>0,91; 2,13</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>703</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1331</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>670</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>536</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2719</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>703</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>2782</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3080</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4401</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3162</t>
+          <t>0; 3797</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2751</t>
+          <t>628; 5491</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>602; 6020</t>
+          <t>0; 1659</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4640</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3732</t>
+          <t>0; 4068</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>637; 5419</t>
+          <t>0; 3501</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2369</t>
+          <t>885; 7669</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4502</t>
+          <t>0; 4567</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 4783</t>
+          <t>0; 4922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>635; 6280</t>
+          <t>683; 6441</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1122; 7295</t>
+          <t>1097; 7421</t>
         </is>
       </c>
     </row>
@@ -2004,37 +2004,37 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,62 +2067,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1515</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2137</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1386</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3432</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1328</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>568</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1515</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2137</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2842</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2705</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>1386</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>3409</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>2842</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2705</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1386</t>
-        </is>
-      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>3799</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4190</t>
+          <t>0; 4732</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2864</t>
+          <t>669; 5918</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>0; 5298</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>889; 9288</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4226</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2893</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0; 2344</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0; 5243</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>662; 6043</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0; 4785</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>856; 10334</t>
+          <t>0; 1657</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>844; 6990</t>
+          <t>718; 6792</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>672; 7162</t>
+          <t>673; 6113</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5358</t>
+          <t>0; 4981</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>853; 10251</t>
+          <t>1220; 10934</t>
         </is>
       </c>
     </row>
@@ -2217,32 +2217,32 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,62 +2275,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>674</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1305</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>701</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1320</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1375</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2625</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>625</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1559</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1375</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2625</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1559</t>
+          <t>1003</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3863</t>
+          <t>0; 3940</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5262</t>
+          <t>0; 4282</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>0; 3256</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5193</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4936</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4067</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4206</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4414</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3178</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0; 8314</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4622</t>
+          <t>0; 4480</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>671; 6590</t>
+          <t>632; 6279</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 3182</t>
+          <t>0; 3007</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 8947</t>
+          <t>0; 4972</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4173</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9712</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2574</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>2385</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>4677</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>4489</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3052</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4173</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9712</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2500</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>3170</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5655</t>
+          <t>5744</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>636; 5947</t>
+          <t>1907; 9029</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1904; 9139</t>
+          <t>5304; 17140</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1963; 9517</t>
+          <t>630; 6208</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>816; 8305</t>
+          <t>738; 7221</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1885; 8700</t>
+          <t>774; 5966</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5243; 15746</t>
+          <t>1901; 9333</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>631; 6280</t>
+          <t>2005; 8518</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>802; 7561</t>
+          <t>854; 7933</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3190; 11579</t>
+          <t>3214; 11976</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9123; 22208</t>
+          <t>8678; 21783</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3620; 12076</t>
+          <t>3875; 12489</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2419; 11283</t>
+          <t>2563; 12396</t>
         </is>
       </c>
     </row>
@@ -2623,32 +2623,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1364</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1671</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>2627</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>3557</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>2125</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2114</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>726</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1364</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2135</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>3641</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>864; 6742</t>
+          <t>0; 4736</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1273; 8041</t>
+          <t>0; 4918</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>609; 6142</t>
+          <t>651; 5636</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>405; 6145</t>
+          <t>295; 4952</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3641</t>
+          <t>598; 6330</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4844</t>
+          <t>1310; 8249</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>650; 5668</t>
+          <t>606; 5729</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>394; 5361</t>
+          <t>508; 6235</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1218; 8364</t>
+          <t>1220; 7645</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2144; 9614</t>
+          <t>2075; 9769</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1475; 8681</t>
+          <t>1730; 8982</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1506; 8999</t>
+          <t>1411; 8656</t>
         </is>
       </c>
     </row>
@@ -2831,32 +2831,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2899,54 +2899,54 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1326</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>564</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>726</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>1326</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>863</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>726</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1326</t>
-        </is>
-      </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
           <t>1214</t>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1237</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>0; 3595</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4485</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3710</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4524</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>0; 2327</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>0; 2229</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>0; 4321</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0; 4641</t>
-        </is>
-      </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 2721</t>
+          <t>0; 2882</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4358</t>
+          <t>0; 1566</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 4050</t>
+          <t>0; 3638</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 4697</t>
+          <t>0; 3996</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 3752</t>
+          <t>0; 3744</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 4546</t>
+          <t>0; 5363</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>7842</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>16561</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>9313</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>9876</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>8345</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>10777</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>7714</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>8698</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>7842</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>16561</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>9313</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>8628</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>19354</t>
+          <t>18504</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4301; 13632</t>
+          <t>4217; 13680</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5987; 17027</t>
+          <t>10749; 24611</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4234; 13572</t>
+          <t>5321; 15137</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4440; 14243</t>
+          <t>5026; 18097</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4031; 13485</t>
+          <t>4774; 14207</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10719; 24458</t>
+          <t>6404; 17081</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5211; 15460</t>
+          <t>4165; 13100</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5551; 20229</t>
+          <t>4658; 14832</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10422; 23671</t>
+          <t>10882; 23868</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19447; 36892</t>
+          <t>18950; 35857</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11184; 24478</t>
+          <t>11142; 24588</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>12704; 28012</t>
+          <t>11909; 27867</t>
         </is>
       </c>
     </row>
